--- a/Report_Presentation/Cost_Revenue_Analysis.xlsx
+++ b/Report_Presentation/Cost_Revenue_Analysis.xlsx
@@ -1,26 +1,114 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gpiga\Desktop\EK505_Final_Project\Report_Presentation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B987EC2B-490E-4216-A034-5D74BFE053E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="10812" yWindow="96" windowWidth="12216" windowHeight="13092" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+  <si>
+    <t>Astronaut EVA Hours / Year</t>
+  </si>
+  <si>
+    <t>Astronaut Amortized Cost / Hour</t>
+  </si>
+  <si>
+    <t>Assumed % inspection</t>
+  </si>
+  <si>
+    <t>Inspection cost / year</t>
+  </si>
+  <si>
+    <t>Number of astronauts / EVA</t>
+  </si>
+  <si>
+    <t>Assumed annual value of ISS experiments per year</t>
+  </si>
+  <si>
+    <t>Assumed lost time % / year</t>
+  </si>
+  <si>
+    <t>Value lost per year</t>
+  </si>
+  <si>
+    <t>Expected Platform Cost</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>From NASA documentation</t>
+  </si>
+  <si>
+    <t>Derived from NASA documentation</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Assumed</t>
+  </si>
+  <si>
+    <t>Payback period</t>
+  </si>
+  <si>
+    <t>We expect to be able to reach 1/2 the cost of satellite servicing hardware</t>
+  </si>
+  <si>
+    <t>Total cost to NASA per year (total potential revenue for Ark Robotics / year)</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Derived from NASA research budget and other grants. Includes all NSF and other grants dedicated to ISS research</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +116,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +153,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +475,149 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:D17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="42.5546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" style="7" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>140</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6">
+        <f>C3*C4*C6*C5</f>
+        <v>19600000</v>
+      </c>
+      <c r="D7" s="4"/>
+    </row>
+    <row r="9" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="6">
+        <v>200000000</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6">
+        <f>C9*C10</f>
+        <v>20000000</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="13" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6">
+        <f>C7+C11</f>
+        <v>39600000</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="15" spans="2:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <f>100000000*0.5</f>
+        <v>50000000</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5">
+        <f>C15/C13</f>
+        <v>1.2626262626262625</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>